--- a/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
+++ b/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
@@ -868,7 +868,7 @@
       <c r="G8" s="24" t="n"/>
       <c r="H8" s="24" t="n"/>
       <c r="I8" s="38" t="n">
-        <v>24000000</v>
+        <v>14400000</v>
       </c>
       <c r="J8" s="39" t="n">
         <v>3.2667</v>
@@ -905,7 +905,7 @@
       <c r="G9" s="24" t="n"/>
       <c r="H9" s="24" t="n"/>
       <c r="I9" s="38" t="n">
-        <v>8000000</v>
+        <v>4800000</v>
       </c>
       <c r="J9" s="39" t="n">
         <v>4.2727</v>

--- a/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
+++ b/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -695,6 +695,11 @@
           <t>Descripción</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28.5" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -731,6 +736,11 @@
           <t>Teaser en IG/TikTok, comunicado a blogs de Bogotá y semana de apertura con gaseosa gratis en combo.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Build awareness at launch</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -767,6 +777,11 @@
           <t>Volantes y degustaciones en oficinas y universidades; aviso de la garantía de satisfacción.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Build awareness at launch</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -804,6 +819,11 @@
           <t>Publica solo martes y viernes (104 días/año), no a diario: videos de producto, detrás del mostrador y combos.</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Stay visible online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -841,6 +861,11 @@
           <t>Fotos, horarios, menú y solicitud de reseñas todo el año.</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Stay visible online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -878,6 +903,11 @@
           <t>Anuncios pagados en un radio alrededor de la tienda.</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Stay visible online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -915,6 +945,11 @@
           <t>QR en empaques y recibos: síguenos + 10% en la próxima compra.</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Stay visible online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -952,6 +987,11 @@
           <t>Pedidos al por mayor para oficinas cercanas por WhatsApp.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Drive repeat orders</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -988,6 +1028,11 @@
           <t>Referido y cliente reciben papas gratis en su siguiente pedido.</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Drive repeat orders</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1024,6 +1069,11 @@
           <t>14 feb: 2 combos con 20% de descuento.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Capture seasonal demand</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1060,6 +1110,11 @@
           <t>Party Pack para reuniones de oficina y familia.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Capture seasonal demand</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1101,6 +1156,11 @@
       <c r="K14" s="27" t="inlineStr">
         <is>
           <t>Stand en campus con muestras gratis al inicio de cada semestre.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Engage the university community</t>
         </is>
       </c>
     </row>

--- a/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
+++ b/Plan_Campanas_Doner_Street_2027_Ajustado.xlsx
@@ -851,7 +851,7 @@
       <c r="G7" s="24" t="n"/>
       <c r="H7" s="24" t="n"/>
       <c r="I7" s="38" t="n">
-        <v>1200000</v>
+        <v>500000</v>
       </c>
       <c r="J7" s="39" t="n">
         <v>5.4</v>
@@ -977,7 +977,7 @@
       <c r="G10" s="24" t="n"/>
       <c r="H10" s="24" t="n"/>
       <c r="I10" s="38" t="n">
-        <v>4000000</v>
+        <v>2900000</v>
       </c>
       <c r="J10" s="39" t="n">
         <v>3.389</v>
